--- a/artfynd/A 17092-2022 artfynd.xlsx
+++ b/artfynd/A 17092-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17092-2022 artfynd.xlsx
+++ b/artfynd/A 17092-2022 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111354726</v>
+        <v>111354025</v>
       </c>
       <c r="B2" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555138.3841980774</v>
+        <v>555155</v>
       </c>
       <c r="R2" t="n">
-        <v>6999122.632572887</v>
+        <v>6999254</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,24 +744,9 @@
           <t>2023-08-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>18:59</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>18:59</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,37 +773,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111355254</v>
+        <v>111354546</v>
       </c>
       <c r="B3" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555272.5859257083</v>
+        <v>555145</v>
       </c>
       <c r="R3" t="n">
-        <v>6999014.46986856</v>
+        <v>6999173</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,19 +842,14 @@
           <t>2023-08-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>19:06</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-08</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>19:06</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,37 +876,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111354809</v>
+        <v>111354189</v>
       </c>
       <c r="B4" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555164.2519777509</v>
+        <v>555134</v>
       </c>
       <c r="R4" t="n">
-        <v>6999120.809599082</v>
+        <v>6999255</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,24 +945,9 @@
           <t>2023-08-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>19:06</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>19:06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,12 +977,7 @@
         <v>111355135</v>
       </c>
       <c r="B5" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1065,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555276.0359517796</v>
+        <v>555276</v>
       </c>
       <c r="R5" t="n">
-        <v>6998998.232622715</v>
+        <v>6998998</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1137,15 +1082,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111354189</v>
+        <v>111355197</v>
       </c>
       <c r="B6" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555134.7763198819</v>
+        <v>555281</v>
       </c>
       <c r="R6" t="n">
-        <v>6999254.742998262</v>
+        <v>6999022</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,7 +1153,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1163,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,12 +1193,7 @@
         <v>111355227</v>
       </c>
       <c r="B7" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555268.7908350837</v>
+        <v>555268</v>
       </c>
       <c r="R7" t="n">
-        <v>6999024.363821026</v>
+        <v>6999024</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1363,15 +1298,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111355197</v>
+        <v>111355254</v>
       </c>
       <c r="B8" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,10 +1334,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555280.6270040129</v>
+        <v>555273</v>
       </c>
       <c r="R8" t="n">
-        <v>6999021.397055306</v>
+        <v>6999014</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1479,12 +1409,7 @@
         <v>111355282</v>
       </c>
       <c r="B9" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555252.2533465028</v>
+        <v>555252</v>
       </c>
       <c r="R9" t="n">
-        <v>6999037.209103072</v>
+        <v>6999037</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1592,12 +1517,7 @@
         <v>111355331</v>
       </c>
       <c r="B10" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,10 +1550,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555224.1634512447</v>
+        <v>555225</v>
       </c>
       <c r="R10" t="n">
-        <v>6999062.984709017</v>
+        <v>6999063</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1702,15 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111354546</v>
+        <v>111355391</v>
       </c>
       <c r="B11" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,21 +1633,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1743,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555144.7642560177</v>
+        <v>555215</v>
       </c>
       <c r="R11" t="n">
-        <v>6999173.89047078</v>
+        <v>6999055</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1693,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,12 +1703,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,37 +1730,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111355391</v>
+        <v>111354696</v>
       </c>
       <c r="B12" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1861,10 +1766,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555215.2391852245</v>
+        <v>555138</v>
       </c>
       <c r="R12" t="n">
-        <v>6999054.684715276</v>
+        <v>6999122</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1894,19 +1799,14 @@
           <t>2023-08-08</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>19:06</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-08-08</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>19:06</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,37 +1833,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111354025</v>
+        <v>111354809</v>
       </c>
       <c r="B13" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1974,10 +1869,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555154.7369911602</v>
+        <v>555165</v>
       </c>
       <c r="R13" t="n">
-        <v>6999253.724818715</v>
+        <v>6999121</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2009,7 +1904,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2019,7 +1914,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 17092-2022 artfynd.xlsx
+++ b/artfynd/A 17092-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111354025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -873,6 +883,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111354546</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111354189</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111355135</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111355197</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1295,6 +1325,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111355227</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1403,6 +1438,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111355254</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1511,6 +1551,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111355282</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1619,6 +1664,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111355331</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1727,6 +1777,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111355391</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1830,6 +1885,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111354696</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1943,8 +2003,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111354809</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>